--- a/arg_urls.xlsx
+++ b/arg_urls.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="757">
   <si>
     <t>x</t>
   </si>
@@ -926,6 +926,231 @@
     <t>303</t>
   </si>
   <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>323</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
+    <t>325</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>327</t>
+  </si>
+  <si>
+    <t>328</t>
+  </si>
+  <si>
+    <t>329</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>331</t>
+  </si>
+  <si>
+    <t>332</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>334</t>
+  </si>
+  <si>
+    <t>335</t>
+  </si>
+  <si>
+    <t>336</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>338</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>348</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>351</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>356</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>358</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>361</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>367</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>373</t>
+  </si>
+  <si>
+    <t>374</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4fefca20/Sarmiento-Instituto-May-10-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -947,12 +1172,12 @@
     <t>https://fbref.com/en/matches/60f2f48f/Newells-Old-Boys-Platense-May-10-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f1dfe976/Tigre-Estudiantes-LP-May-12-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/b005f9fa/Deportivo-Riestra-San-Lorenzo-May-12-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f1dfe976/Tigre-Estudiantes-LP-May-12-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/73d783e1/Lanus-Independiente-Rivadavia-May-12-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -986,12 +1211,12 @@
     <t>https://fbref.com/en/matches/ace9365f/Platense-Independiente-May-19-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/8ab20306/Banfield-Huracan-May-19-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/8000169a/Talleres-Atletico-Tucuman-May-19-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/8ab20306/Banfield-Huracan-May-19-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/19095fe5/Central-Cordoba-SdE-Boca-Juniors-May-19-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1025,12 +1250,12 @@
     <t>https://fbref.com/en/matches/54fc7d8f/Boca-Juniors-Talleres-May-25-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f4fe03b6/Lanus-Estudiantes-LP-May-24-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/671b79b8/Belgrano-Central-Cordoba-SdE-May-24-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f4fe03b6/Lanus-Estudiantes-LP-May-24-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/9334b993/Huracan-Instituto-May-26-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1052,12 +1277,12 @@
     <t>https://fbref.com/en/matches/801f6f6c/Racing-Club-Deportivo-Riestra-June-1-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/c1f8681d/Velez-Sarsfield-Atletico-Tucuman-June-1-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/7b021373/Belgrano-Argentinos-Juniors-June-1-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c1f8681d/Velez-Sarsfield-Atletico-Tucuman-June-1-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/78ae091a/Platense-Boca-Juniors-June-2-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1067,30 +1292,30 @@
     <t>https://fbref.com/en/matches/f904d738/Central-Cordoba-SdE-Talleres-June-2-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7585cbde/River-Plate-Tigre-June-2-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/472ee950/Instituto-Gimnasia-y-Esgrima-LP-June-2-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7585cbde/River-Plate-Tigre-June-2-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8522ec85/San-Lorenzo-Sarmiento-June-3-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/e2855404/Barracas-Central-Huracan-June-4-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/de3d6cea/Independiente-Rivadavia-Union-June-4-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/50c2cfe4/Banfield-Newells-Old-Boys-June-4-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/de3d6cea/Independiente-Rivadavia-Union-June-4-2024-Liga-Profesional-Argentina</t>
+    <t>https://fbref.com/en/matches/bf949c92/Estudiantes-LP-Godoy-Cruz-June-3-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/328a5274/Defensa-y-Justicia-Independiente-June-3-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/bf949c92/Estudiantes-LP-Godoy-Cruz-June-3-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/086ba2d9/Godoy-Cruz-Rosario-Central-June-12-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1100,12 +1325,12 @@
     <t>https://fbref.com/en/matches/6020b448/Deportivo-Riestra-River-Plate-June-13-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f33a3e2d/Sarmiento-Estudiantes-LP-June-13-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6ea5e3ab/Tigre-Belgrano-June-13-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f33a3e2d/Sarmiento-Estudiantes-LP-June-13-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/4aec9ad3/Independiente-Banfield-June-12-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1118,12 +1343,12 @@
     <t>https://fbref.com/en/matches/8ca805f4/Boca-Juniors-Velez-Sarsfield-June-14-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/8e5aa607/Newells-Old-Boys-Instituto-June-13-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/01141056/Lanus-Racing-Club-June-13-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/8e5aa607/Newells-Old-Boys-Instituto-June-13-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/54a63184/Union-San-Lorenzo-June-15-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1178,39 +1403,39 @@
     <t>https://fbref.com/en/matches/d07a7bb8/Deportivo-Riestra-Argentinos-Juniors-July-23-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/34dd72a6/Gimnasia-y-Esgrima-LP-San-Lorenzo-July-23-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/14cb6425/Newells-Old-Boys-Independiente-Rivadavia-July-23-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/34dd72a6/Gimnasia-y-Esgrima-LP-San-Lorenzo-July-23-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/0bf1640f/Talleres-Defensa-y-Justicia-July-24-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/883ccf07/Sarmiento-Racing-Club-July-24-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/dcdb5607/Huracan-Estudiantes-LP-July-24-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2be95118/Godoy-Cruz-River-Plate-July-24-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/dcdb5607/Huracan-Estudiantes-LP-July-24-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/20a8266f/Independiente-Barracas-Central-July-23-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/df28bded/Lanus-Belgrano-July-25-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/8591b350/Platense-Velez-Sarsfield-July-25-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/df28bded/Lanus-Belgrano-July-25-2024-Liga-Profesional-Argentina</t>
+    <t>https://fbref.com/en/matches/83cab639/Atletico-Tucuman-Instituto-July-25-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/77ddafb0/Tigre-Central-Cordoba-SdE-July-25-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/83cab639/Atletico-Tucuman-Instituto-July-25-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/9a2c4c24/Independiente-Rivadavia-Independiente-July-27-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1220,12 +1445,12 @@
     <t>https://fbref.com/en/matches/42fd7007/Rosario-Central-Huracan-July-27-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7ce1fceb/Banfield-Talleres-July-28-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4032e394/Estudiantes-LP-Gimnasia-y-Esgrima-LP-July-28-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7ce1fceb/Banfield-Talleres-July-28-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e087d92a/Racing-Club-Union-July-28-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1241,12 +1466,12 @@
     <t>https://fbref.com/en/matches/696a3f01/Defensa-y-Justicia-Platense-July-29-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/dd894773/Central-Cordoba-SdE-Velez-Sarsfield-July-29-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/a3150d16/Tigre-Deportivo-Riestra-July-29-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/dd894773/Central-Cordoba-SdE-Velez-Sarsfield-July-29-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/9cffaca2/Belgrano-Godoy-Cruz-July-29-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1262,12 +1487,12 @@
     <t>https://fbref.com/en/matches/22fa807d/Newells-Old-Boys-Estudiantes-LP-August-2-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f1040d70/Godoy-Cruz-Argentinos-Juniors-August-3-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/c77c41d0/Velez-Sarsfield-Defensa-y-Justicia-August-3-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f1040d70/Godoy-Cruz-Argentinos-Juniors-August-3-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/6a4cc56c/Talleres-Instituto-August-3-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1277,12 +1502,12 @@
     <t>https://fbref.com/en/matches/d38a0131/Huracan-Racing-Club-August-3-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/41afaec5/Union-River-Plate-August-4-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0d0c8959/Sarmiento-Belgrano-August-4-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/41afaec5/Union-River-Plate-August-4-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c7fdaf15/Boca-Juniors-Barracas-Central-August-4-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1328,12 +1553,12 @@
     <t>https://fbref.com/en/matches/2a432d07/Racing-Club-Gimnasia-y-Esgrima-LP-August-9-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/4f0c1fe0/Central-Cordoba-SdE-Defensa-y-Justicia-August-11-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0e4e4d6d/Instituto-Platense-August-11-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4f0c1fe0/Central-Cordoba-SdE-Defensa-y-Justicia-August-11-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8f5aefe1/Banfield-Velez-Sarsfield-August-11-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1355,12 +1580,12 @@
     <t>https://fbref.com/en/matches/eddfdacc/Gimnasia-y-Esgrima-LP-River-Plate-August-17-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e2d12b82/Velez-Sarsfield-Instituto-August-17-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/56dc55c2/Talleres-Independiente-Rivadavia-August-17-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e2d12b82/Velez-Sarsfield-Instituto-August-17-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/b4f71c28/Newells-Old-Boys-Racing-Club-August-16-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1376,12 +1601,12 @@
     <t>https://fbref.com/en/matches/ffa26e9e/Huracan-Belgrano-August-18-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/bdd0f84e/Godoy-Cruz-Deportivo-Riestra-August-19-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/25085b0b/Union-Argentinos-Juniors-August-19-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/bdd0f84e/Godoy-Cruz-Deportivo-Riestra-August-19-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/dc1564fb/Defensa-y-Justicia-Banfield-August-19-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1400,12 +1625,12 @@
     <t>https://fbref.com/en/matches/97afa365/Tigre-Union-August-24-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/73d4ae14/San-Lorenzo-Talleres-August-25-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6bc1f192/Lanus-Godoy-Cruz-August-25-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/73d4ae14/San-Lorenzo-Talleres-August-25-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/bf1c71ad/Racing-Club-Independiente-August-25-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1430,12 +1655,12 @@
     <t>https://fbref.com/en/matches/cdf091e6/Sarmiento-Lanus-August-30-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/eff697f6/Defensa-y-Justicia-Barracas-Central-August-31-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/504dcecd/Newells-Old-Boys-Belgrano-August-31-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/eff697f6/Defensa-y-Justicia-Barracas-Central-August-31-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8663e237/Talleres-Estudiantes-LP-August-31-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1472,12 +1697,12 @@
     <t>https://fbref.com/en/matches/ea3c5612/Deportivo-Riestra-Huracan-September-13-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7aade4a2/Central-Cordoba-SdE-Instituto-September-13-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/15a64ce2/Lanus-Union-September-13-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7aade4a2/Central-Cordoba-SdE-Instituto-September-13-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e6778aef/San-Lorenzo-Velez-Sarsfield-September-14-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1526,45 +1751,45 @@
     <t>https://fbref.com/en/matches/c3a59da8/Instituto-Barracas-Central-September-21-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/914db8ba/Huracan-Lanus-September-22-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5563b539/Independiente-Argentinos-Juniors-September-22-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/914db8ba/Huracan-Lanus-September-22-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/f4fc1967/Talleres-Racing-Club-September-22-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d284e695/Atletico-Tucuman-Belgrano-September-22-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/71fa5023/Platense-Rosario-Central-September-22-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d284e695/Atletico-Tucuman-Belgrano-September-22-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/0924d9ff/Defensa-y-Justicia-San-Lorenzo-September-21-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/0dfd6912/Sarmiento-Central-Cordoba-SdE-September-23-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/c86c1f48/Velez-Sarsfield-Estudiantes-LP-September-23-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4f669270/Banfield-Independiente-Rivadavia-September-23-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c86c1f48/Velez-Sarsfield-Estudiantes-LP-September-23-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/1502c209/Deportivo-Riestra-Newells-Old-Boys-September-27-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1531fcae/San-Lorenzo-Banfield-September-28-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9554f7af/Godoy-Cruz-Huracan-September-28-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5eb5ad2d/Estudiantes-LP-Defensa-y-Justicia-September-28-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9554f7af/Godoy-Cruz-Huracan-September-28-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/b7c78896/Belgrano-Boca-Juniors-September-28-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1652,12 +1877,12 @@
     <t>https://fbref.com/en/matches/9a278bf0/Lanus-Independiente-October-18-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e88609b3/Racing-Club-Defensa-y-Justicia-October-19-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0c1202e7/Belgrano-Platense-October-19-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e88609b3/Racing-Club-Defensa-y-Justicia-October-19-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8f6ce0d7/Tigre-Boca-Juniors-October-19-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1667,12 +1892,12 @@
     <t>https://fbref.com/en/matches/6373481e/Argentinos-Juniors-Talleres-October-20-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/397460e4/Estudiantes-LP-Instituto-October-20-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/31214cd9/Rosario-Central-Banfield-October-20-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/397460e4/Estudiantes-LP-Instituto-October-20-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/d31edbf6/San-Lorenzo-Barracas-Central-October-20-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1685,12 +1910,12 @@
     <t>https://fbref.com/en/matches/593c491b/Barracas-Central-Estudiantes-LP-October-25-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/8c28f8c8/Instituto-Rosario-Central-October-26-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/654d2b62/Newells-Old-Boys-Sarmiento-October-26-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/8c28f8c8/Instituto-Rosario-Central-October-26-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/00bfef50/Independiente-Godoy-Cruz-October-26-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1715,33 +1940,33 @@
     <t>https://fbref.com/en/matches/76e7b902/Gimnasia-y-Esgrima-LP-Union-October-28-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/c700fbf1/Atletico-Tucuman-Lanus-October-27-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/aa843def/Talleres-Tigre-October-27-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c700fbf1/Atletico-Tucuman-Lanus-October-27-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/77ac090a/Huracan-Central-Cordoba-SdE-October-28-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/181c82ff/Estudiantes-LP-Independiente-Rivadavia-October-31-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0e9415b9/Sarmiento-Independiente-October-31-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/181c82ff/Estudiantes-LP-Independiente-Rivadavia-October-31-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/89cff9db/Central-Cordoba-SdE-San-Lorenzo-November-1-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/f79c470e/Huracan-Gimnasia-y-Esgrima-LP-November-1-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/caac37f7/Godoy-Cruz-Atletico-Tucuman-October-31-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/7f966f29/Rosario-Central-Barracas-Central-October-31-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/caac37f7/Godoy-Cruz-Atletico-Tucuman-October-31-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/67f24360/Deportivo-Riestra-Talleres-November-2-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1769,12 +1994,12 @@
     <t>https://fbref.com/en/matches/25e56b66/Atletico-Tucuman-Sarmiento-November-4-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f56c7219/Gimnasia-y-Esgrima-LP-Central-Cordoba-SdE-November-5-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/71d88c3f/San-Lorenzo-Estudiantes-LP-November-5-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f56c7219/Gimnasia-y-Esgrima-LP-Central-Cordoba-SdE-November-5-2024-Liga-Profesional-Argentina</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/b842069d/Independiente-Rivadavia-Rosario-Central-November-4-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
@@ -1832,7 +2057,232 @@
     <t>https://fbref.com/en/matches/7873027a/Huracan-Independiente-November-9-2024-Liga-Profesional-Argentina</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/2586207f/Deportivo-Riestra-Velez-Sarsfield-November-11-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fa3a83d2/Lanus-Platense-November-11-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/30b52140/Tigre-Defensa-y-Justicia-November-11-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/aff72102/Sarmiento-Boca-Juniors-November-10-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/069edfec/Belgrano-Instituto-November-11-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/83b23b0e/Argentinos-Juniors-Banfield-November-11-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cd00c95f/San-Lorenzo-Racing-Club-November-17-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d461fc44/Banfield-Tigre-November-18-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3945d907/Defensa-y-Justicia-Deportivo-Riestra-November-18-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9576ca03/Platense-Godoy-Cruz-November-18-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/732c1f14/Instituto-Argentinos-Juniors-November-18-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6a950b2c/Atletico-Tucuman-Huracan-November-18-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6fbd3cf8/Newells-Old-Boys-Central-Cordoba-SdE-November-20-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f332ec88/Estudiantes-LP-Rosario-Central-November-20-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2f53e7c6/Velez-Sarsfield-Lanus-November-20-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f4fcd246/Barracas-Central-Belgrano-November-21-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/47b14aa5/Independiente-Gimnasia-y-Esgrima-LP-November-21-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/68849182/Talleres-Sarmiento-November-21-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/17f55a63/Boca-Juniors-Union-November-20-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/efbf6590/Independiente-Rivadavia-River-Plate-November-21-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8291b146/Tigre-Instituto-November-23-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9138c74d/Deportivo-Riestra-Banfield-November-24-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d0650e33/Gimnasia-y-Esgrima-LP-Atletico-Tucuman-November-24-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1f6bd28b/Godoy-Cruz-Velez-Sarsfield-November-24-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/68013eeb/Huracan-Boca-Juniors-November-23-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/36d000c1/Central-Cordoba-SdE-Rosario-Central-November-25-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/98008ab8/Lanus-Defensa-y-Justicia-November-24-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8d65a617/Newells-Old-Boys-Independiente-November-26-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8fd8d4f3/Argentinos-Juniors-Barracas-Central-November-25-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5a026294/Belgrano-Independiente-Rivadavia-November-25-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/eae614bc/Union-Talleres-November-26-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ecc34189/Sarmiento-Platense-November-26-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7ef45c6e/San-Lorenzo-Belgrano-November-29-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b02311bf/Banfield-Lanus-November-30-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/15ad80c6/Rosario-Central-Racing-Club-November-30-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/81114058/Estudiantes-LP-River-Plate-November-29-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6e2d0167/Independiente-Central-Cordoba-SdE-December-1-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e83572e9/Velez-Sarsfield-Sarmiento-December-1-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9ad12c81/Instituto-Deportivo-Riestra-November-30-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/57ba1b33/Defensa-y-Justicia-Godoy-Cruz-November-30-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fd7839eb/Barracas-Central-Tigre-December-2-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/87fbf64e/Platense-Union-December-2-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fb51522a/Talleres-Huracan-December-2-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a5967a27/Boca-Juniors-Gimnasia-y-Esgrima-LP-December-1-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c0d6792f/Independiente-Rivadavia-Argentinos-Juniors-December-2-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/92763dfa/Atletico-Tucuman-Newells-Old-Boys-December-2-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ed17e6c7/Racing-Club-Estudiantes-LP-December-4-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/871861d6/River-Plate-San-Lorenzo-December-4-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ba6b01b7/Deportivo-Riestra-Barracas-Central-December-6-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/72283c29/Sarmiento-Defensa-y-Justicia-December-6-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8c3927a7/Lanus-Instituto-December-7-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0b9afdbb/Union-Velez-Sarsfield-December-7-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ceadbae3/Gimnasia-y-Esgrima-LP-Talleres-December-8-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/76582910/Godoy-Cruz-Banfield-December-8-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a2dfcd21/River-Plate-Rosario-Central-December-8-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e30de86d/Central-Cordoba-SdE-Racing-Club-December-7-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fb96c7b1/Tigre-Independiente-Rivadavia-December-9-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/16b6b735/Belgrano-Estudiantes-LP-December-9-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/127c76b2/Argentinos-Juniors-San-Lorenzo-December-9-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/63f6d14f/Newells-Old-Boys-Boca-Juniors-December-8-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b0ae9e47/Huracan-Platense-December-9-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3c78b8d0/Independiente-Atletico-Tucuman-December-9-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d3edfa8d/Estudiantes-LP-Argentinos-Juniors-December-13-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1292c078/Barracas-Central-Lanus-December-13-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fba8b246/Instituto-Godoy-Cruz-December-14-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c260d450/Rosario-Central-Belgrano-December-14-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dd08ffc4/Boca-Juniors-Independiente-December-14-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7b8d93b3/San-Lorenzo-Tigre-December-13-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d277d008/Banfield-Sarmiento-December-13-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5339f757/Defensa-y-Justicia-Union-December-15-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/895d5c14/Platense-Gimnasia-y-Esgrima-LP-December-15-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/79c2d995/Velez-Sarsfield-Huracan-December-15-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0b89ba33/Talleres-Newells-Old-Boys-December-15-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5e5f5389/Racing-Club-River-Plate-December-14-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/57e20023/Independiente-Rivadavia-Deportivo-Riestra-December-16-2024-Liga-Profesional-Argentina</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5c4a18f8/Atletico-Tucuman-Central-Cordoba-SdE-December-16-2024-Liga-Profesional-Argentina</t>
   </si>
 </sst>
 </file>
@@ -1891,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3">
@@ -1899,7 +2349,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>305</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4">
@@ -1907,7 +2357,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>306</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5">
@@ -1915,7 +2365,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>307</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6">
@@ -1923,7 +2373,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>308</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7">
@@ -1931,7 +2381,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8">
@@ -1939,7 +2389,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>310</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1947,7 +2397,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>311</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10">
@@ -1955,7 +2405,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>312</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11">
@@ -1963,7 +2413,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>313</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12">
@@ -1971,7 +2421,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>314</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13">
@@ -1979,7 +2429,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>315</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14">
@@ -1987,7 +2437,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>316</v>
+        <v>391</v>
       </c>
     </row>
     <row r="15">
@@ -1995,7 +2445,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>317</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16">
@@ -2003,7 +2453,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>318</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17">
@@ -2011,7 +2461,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>319</v>
+        <v>394</v>
       </c>
     </row>
     <row r="18">
@@ -2019,7 +2469,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>320</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19">
@@ -2027,7 +2477,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>321</v>
+        <v>396</v>
       </c>
     </row>
     <row r="20">
@@ -2035,7 +2485,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>322</v>
+        <v>397</v>
       </c>
     </row>
     <row r="21">
@@ -2043,7 +2493,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>323</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22">
@@ -2051,7 +2501,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>324</v>
+        <v>399</v>
       </c>
     </row>
     <row r="23">
@@ -2059,7 +2509,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>325</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24">
@@ -2067,7 +2517,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>326</v>
+        <v>401</v>
       </c>
     </row>
     <row r="25">
@@ -2075,7 +2525,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>327</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26">
@@ -2083,7 +2533,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>328</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27">
@@ -2091,7 +2541,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>329</v>
+        <v>404</v>
       </c>
     </row>
     <row r="28">
@@ -2099,7 +2549,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>330</v>
+        <v>405</v>
       </c>
     </row>
     <row r="29">
@@ -2107,7 +2557,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>331</v>
+        <v>406</v>
       </c>
     </row>
     <row r="30">
@@ -2115,7 +2565,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>332</v>
+        <v>407</v>
       </c>
     </row>
     <row r="31">
@@ -2123,7 +2573,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>333</v>
+        <v>408</v>
       </c>
     </row>
     <row r="32">
@@ -2131,7 +2581,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>334</v>
+        <v>409</v>
       </c>
     </row>
     <row r="33">
@@ -2139,7 +2589,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>335</v>
+        <v>410</v>
       </c>
     </row>
     <row r="34">
@@ -2147,7 +2597,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>336</v>
+        <v>411</v>
       </c>
     </row>
     <row r="35">
@@ -2155,7 +2605,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>337</v>
+        <v>412</v>
       </c>
     </row>
     <row r="36">
@@ -2163,7 +2613,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>338</v>
+        <v>413</v>
       </c>
     </row>
     <row r="37">
@@ -2171,7 +2621,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>339</v>
+        <v>414</v>
       </c>
     </row>
     <row r="38">
@@ -2179,7 +2629,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>340</v>
+        <v>415</v>
       </c>
     </row>
     <row r="39">
@@ -2187,7 +2637,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>341</v>
+        <v>416</v>
       </c>
     </row>
     <row r="40">
@@ -2195,7 +2645,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>342</v>
+        <v>417</v>
       </c>
     </row>
     <row r="41">
@@ -2203,7 +2653,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>343</v>
+        <v>418</v>
       </c>
     </row>
     <row r="42">
@@ -2211,7 +2661,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>344</v>
+        <v>419</v>
       </c>
     </row>
     <row r="43">
@@ -2219,7 +2669,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>345</v>
+        <v>420</v>
       </c>
     </row>
     <row r="44">
@@ -2227,7 +2677,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>346</v>
+        <v>421</v>
       </c>
     </row>
     <row r="45">
@@ -2235,7 +2685,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>347</v>
+        <v>422</v>
       </c>
     </row>
     <row r="46">
@@ -2243,7 +2693,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>348</v>
+        <v>423</v>
       </c>
     </row>
     <row r="47">
@@ -2251,7 +2701,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>349</v>
+        <v>424</v>
       </c>
     </row>
     <row r="48">
@@ -2259,7 +2709,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>350</v>
+        <v>425</v>
       </c>
     </row>
     <row r="49">
@@ -2267,7 +2717,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>351</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50">
@@ -2275,7 +2725,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>352</v>
+        <v>427</v>
       </c>
     </row>
     <row r="51">
@@ -2283,7 +2733,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>353</v>
+        <v>428</v>
       </c>
     </row>
     <row r="52">
@@ -2291,7 +2741,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>354</v>
+        <v>429</v>
       </c>
     </row>
     <row r="53">
@@ -2299,7 +2749,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>355</v>
+        <v>430</v>
       </c>
     </row>
     <row r="54">
@@ -2307,7 +2757,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>356</v>
+        <v>431</v>
       </c>
     </row>
     <row r="55">
@@ -2315,7 +2765,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>357</v>
+        <v>432</v>
       </c>
     </row>
     <row r="56">
@@ -2323,7 +2773,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>358</v>
+        <v>433</v>
       </c>
     </row>
     <row r="57">
@@ -2331,7 +2781,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>359</v>
+        <v>434</v>
       </c>
     </row>
     <row r="58">
@@ -2339,7 +2789,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>360</v>
+        <v>435</v>
       </c>
     </row>
     <row r="59">
@@ -2347,7 +2797,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>361</v>
+        <v>436</v>
       </c>
     </row>
     <row r="60">
@@ -2355,7 +2805,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>362</v>
+        <v>437</v>
       </c>
     </row>
     <row r="61">
@@ -2363,7 +2813,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>363</v>
+        <v>438</v>
       </c>
     </row>
     <row r="62">
@@ -2371,7 +2821,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>364</v>
+        <v>439</v>
       </c>
     </row>
     <row r="63">
@@ -2379,7 +2829,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>365</v>
+        <v>440</v>
       </c>
     </row>
     <row r="64">
@@ -2387,7 +2837,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>366</v>
+        <v>441</v>
       </c>
     </row>
     <row r="65">
@@ -2395,7 +2845,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>367</v>
+        <v>442</v>
       </c>
     </row>
     <row r="66">
@@ -2403,7 +2853,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>368</v>
+        <v>443</v>
       </c>
     </row>
     <row r="67">
@@ -2411,7 +2861,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>369</v>
+        <v>444</v>
       </c>
     </row>
     <row r="68">
@@ -2419,7 +2869,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>370</v>
+        <v>445</v>
       </c>
     </row>
     <row r="69">
@@ -2427,7 +2877,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>371</v>
+        <v>446</v>
       </c>
     </row>
     <row r="70">
@@ -2435,7 +2885,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>372</v>
+        <v>447</v>
       </c>
     </row>
     <row r="71">
@@ -2443,7 +2893,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>373</v>
+        <v>448</v>
       </c>
     </row>
     <row r="72">
@@ -2451,7 +2901,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>374</v>
+        <v>449</v>
       </c>
     </row>
     <row r="73">
@@ -2459,7 +2909,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>375</v>
+        <v>450</v>
       </c>
     </row>
     <row r="74">
@@ -2467,7 +2917,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>376</v>
+        <v>451</v>
       </c>
     </row>
     <row r="75">
@@ -2475,7 +2925,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>377</v>
+        <v>452</v>
       </c>
     </row>
     <row r="76">
@@ -2483,7 +2933,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>378</v>
+        <v>453</v>
       </c>
     </row>
     <row r="77">
@@ -2491,7 +2941,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>379</v>
+        <v>454</v>
       </c>
     </row>
     <row r="78">
@@ -2499,7 +2949,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>380</v>
+        <v>455</v>
       </c>
     </row>
     <row r="79">
@@ -2507,7 +2957,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>381</v>
+        <v>456</v>
       </c>
     </row>
     <row r="80">
@@ -2515,7 +2965,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>382</v>
+        <v>457</v>
       </c>
     </row>
     <row r="81">
@@ -2523,7 +2973,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>383</v>
+        <v>458</v>
       </c>
     </row>
     <row r="82">
@@ -2531,7 +2981,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>384</v>
+        <v>459</v>
       </c>
     </row>
     <row r="83">
@@ -2539,7 +2989,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>385</v>
+        <v>460</v>
       </c>
     </row>
     <row r="84">
@@ -2547,7 +2997,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>386</v>
+        <v>461</v>
       </c>
     </row>
     <row r="85">
@@ -2555,7 +3005,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>387</v>
+        <v>462</v>
       </c>
     </row>
     <row r="86">
@@ -2563,7 +3013,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>388</v>
+        <v>463</v>
       </c>
     </row>
     <row r="87">
@@ -2571,7 +3021,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>389</v>
+        <v>464</v>
       </c>
     </row>
     <row r="88">
@@ -2579,7 +3029,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>390</v>
+        <v>465</v>
       </c>
     </row>
     <row r="89">
@@ -2587,7 +3037,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>391</v>
+        <v>466</v>
       </c>
     </row>
     <row r="90">
@@ -2595,7 +3045,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>392</v>
+        <v>467</v>
       </c>
     </row>
     <row r="91">
@@ -2603,7 +3053,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>393</v>
+        <v>468</v>
       </c>
     </row>
     <row r="92">
@@ -2611,7 +3061,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>394</v>
+        <v>469</v>
       </c>
     </row>
     <row r="93">
@@ -2619,7 +3069,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>395</v>
+        <v>470</v>
       </c>
     </row>
     <row r="94">
@@ -2627,7 +3077,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>396</v>
+        <v>471</v>
       </c>
     </row>
     <row r="95">
@@ -2635,7 +3085,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>397</v>
+        <v>472</v>
       </c>
     </row>
     <row r="96">
@@ -2643,7 +3093,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>398</v>
+        <v>473</v>
       </c>
     </row>
     <row r="97">
@@ -2651,7 +3101,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>399</v>
+        <v>474</v>
       </c>
     </row>
     <row r="98">
@@ -2659,7 +3109,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>400</v>
+        <v>475</v>
       </c>
     </row>
     <row r="99">
@@ -2667,7 +3117,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>401</v>
+        <v>476</v>
       </c>
     </row>
     <row r="100">
@@ -2675,7 +3125,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>402</v>
+        <v>477</v>
       </c>
     </row>
     <row r="101">
@@ -2683,7 +3133,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>403</v>
+        <v>478</v>
       </c>
     </row>
     <row r="102">
@@ -2691,7 +3141,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>404</v>
+        <v>479</v>
       </c>
     </row>
     <row r="103">
@@ -2699,7 +3149,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>405</v>
+        <v>480</v>
       </c>
     </row>
     <row r="104">
@@ -2707,7 +3157,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>406</v>
+        <v>481</v>
       </c>
     </row>
     <row r="105">
@@ -2715,7 +3165,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>407</v>
+        <v>482</v>
       </c>
     </row>
     <row r="106">
@@ -2723,7 +3173,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>408</v>
+        <v>483</v>
       </c>
     </row>
     <row r="107">
@@ -2731,7 +3181,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>409</v>
+        <v>484</v>
       </c>
     </row>
     <row r="108">
@@ -2739,7 +3189,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>410</v>
+        <v>485</v>
       </c>
     </row>
     <row r="109">
@@ -2747,7 +3197,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>411</v>
+        <v>486</v>
       </c>
     </row>
     <row r="110">
@@ -2755,7 +3205,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>412</v>
+        <v>487</v>
       </c>
     </row>
     <row r="111">
@@ -2763,7 +3213,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>413</v>
+        <v>488</v>
       </c>
     </row>
     <row r="112">
@@ -2771,7 +3221,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>414</v>
+        <v>489</v>
       </c>
     </row>
     <row r="113">
@@ -2779,7 +3229,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>415</v>
+        <v>490</v>
       </c>
     </row>
     <row r="114">
@@ -2787,7 +3237,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>416</v>
+        <v>491</v>
       </c>
     </row>
     <row r="115">
@@ -2795,7 +3245,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>417</v>
+        <v>492</v>
       </c>
     </row>
     <row r="116">
@@ -2803,7 +3253,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>418</v>
+        <v>493</v>
       </c>
     </row>
     <row r="117">
@@ -2811,7 +3261,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>419</v>
+        <v>494</v>
       </c>
     </row>
     <row r="118">
@@ -2819,7 +3269,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>420</v>
+        <v>495</v>
       </c>
     </row>
     <row r="119">
@@ -2827,7 +3277,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>421</v>
+        <v>496</v>
       </c>
     </row>
     <row r="120">
@@ -2835,7 +3285,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>422</v>
+        <v>497</v>
       </c>
     </row>
     <row r="121">
@@ -2843,7 +3293,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>423</v>
+        <v>498</v>
       </c>
     </row>
     <row r="122">
@@ -2851,7 +3301,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>424</v>
+        <v>499</v>
       </c>
     </row>
     <row r="123">
@@ -2859,7 +3309,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>425</v>
+        <v>500</v>
       </c>
     </row>
     <row r="124">
@@ -2867,7 +3317,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>426</v>
+        <v>501</v>
       </c>
     </row>
     <row r="125">
@@ -2875,7 +3325,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>427</v>
+        <v>502</v>
       </c>
     </row>
     <row r="126">
@@ -2883,7 +3333,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>428</v>
+        <v>503</v>
       </c>
     </row>
     <row r="127">
@@ -2891,7 +3341,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>429</v>
+        <v>504</v>
       </c>
     </row>
     <row r="128">
@@ -2899,7 +3349,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>430</v>
+        <v>505</v>
       </c>
     </row>
     <row r="129">
@@ -2907,7 +3357,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>431</v>
+        <v>506</v>
       </c>
     </row>
     <row r="130">
@@ -2915,7 +3365,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>432</v>
+        <v>507</v>
       </c>
     </row>
     <row r="131">
@@ -2923,7 +3373,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>433</v>
+        <v>508</v>
       </c>
     </row>
     <row r="132">
@@ -2931,7 +3381,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>434</v>
+        <v>509</v>
       </c>
     </row>
     <row r="133">
@@ -2939,7 +3389,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>435</v>
+        <v>510</v>
       </c>
     </row>
     <row r="134">
@@ -2947,7 +3397,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>436</v>
+        <v>511</v>
       </c>
     </row>
     <row r="135">
@@ -2955,7 +3405,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>437</v>
+        <v>512</v>
       </c>
     </row>
     <row r="136">
@@ -2963,7 +3413,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>438</v>
+        <v>513</v>
       </c>
     </row>
     <row r="137">
@@ -2971,7 +3421,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>439</v>
+        <v>514</v>
       </c>
     </row>
     <row r="138">
@@ -2979,7 +3429,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>440</v>
+        <v>515</v>
       </c>
     </row>
     <row r="139">
@@ -2987,7 +3437,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>441</v>
+        <v>516</v>
       </c>
     </row>
     <row r="140">
@@ -2995,7 +3445,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>442</v>
+        <v>517</v>
       </c>
     </row>
     <row r="141">
@@ -3003,7 +3453,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>443</v>
+        <v>518</v>
       </c>
     </row>
     <row r="142">
@@ -3011,7 +3461,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>444</v>
+        <v>519</v>
       </c>
     </row>
     <row r="143">
@@ -3019,7 +3469,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>445</v>
+        <v>520</v>
       </c>
     </row>
     <row r="144">
@@ -3027,7 +3477,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>446</v>
+        <v>521</v>
       </c>
     </row>
     <row r="145">
@@ -3035,7 +3485,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>447</v>
+        <v>522</v>
       </c>
     </row>
     <row r="146">
@@ -3043,7 +3493,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>448</v>
+        <v>523</v>
       </c>
     </row>
     <row r="147">
@@ -3051,7 +3501,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>449</v>
+        <v>524</v>
       </c>
     </row>
     <row r="148">
@@ -3059,7 +3509,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>450</v>
+        <v>525</v>
       </c>
     </row>
     <row r="149">
@@ -3067,7 +3517,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>451</v>
+        <v>526</v>
       </c>
     </row>
     <row r="150">
@@ -3075,7 +3525,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>452</v>
+        <v>527</v>
       </c>
     </row>
     <row r="151">
@@ -3083,7 +3533,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>453</v>
+        <v>528</v>
       </c>
     </row>
     <row r="152">
@@ -3091,7 +3541,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>454</v>
+        <v>529</v>
       </c>
     </row>
     <row r="153">
@@ -3099,7 +3549,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>455</v>
+        <v>530</v>
       </c>
     </row>
     <row r="154">
@@ -3107,7 +3557,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>456</v>
+        <v>531</v>
       </c>
     </row>
     <row r="155">
@@ -3115,7 +3565,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>457</v>
+        <v>532</v>
       </c>
     </row>
     <row r="156">
@@ -3123,7 +3573,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>458</v>
+        <v>533</v>
       </c>
     </row>
     <row r="157">
@@ -3131,7 +3581,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>459</v>
+        <v>534</v>
       </c>
     </row>
     <row r="158">
@@ -3139,7 +3589,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>460</v>
+        <v>535</v>
       </c>
     </row>
     <row r="159">
@@ -3147,7 +3597,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>461</v>
+        <v>536</v>
       </c>
     </row>
     <row r="160">
@@ -3155,7 +3605,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>462</v>
+        <v>537</v>
       </c>
     </row>
     <row r="161">
@@ -3163,7 +3613,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>463</v>
+        <v>538</v>
       </c>
     </row>
     <row r="162">
@@ -3171,7 +3621,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>464</v>
+        <v>539</v>
       </c>
     </row>
     <row r="163">
@@ -3179,7 +3629,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>465</v>
+        <v>540</v>
       </c>
     </row>
     <row r="164">
@@ -3187,7 +3637,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>466</v>
+        <v>541</v>
       </c>
     </row>
     <row r="165">
@@ -3195,7 +3645,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>467</v>
+        <v>542</v>
       </c>
     </row>
     <row r="166">
@@ -3203,7 +3653,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>468</v>
+        <v>543</v>
       </c>
     </row>
     <row r="167">
@@ -3211,7 +3661,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>469</v>
+        <v>544</v>
       </c>
     </row>
     <row r="168">
@@ -3219,7 +3669,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>470</v>
+        <v>545</v>
       </c>
     </row>
     <row r="169">
@@ -3227,7 +3677,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>471</v>
+        <v>546</v>
       </c>
     </row>
     <row r="170">
@@ -3235,7 +3685,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>472</v>
+        <v>547</v>
       </c>
     </row>
     <row r="171">
@@ -3243,7 +3693,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>473</v>
+        <v>548</v>
       </c>
     </row>
     <row r="172">
@@ -3251,7 +3701,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>474</v>
+        <v>549</v>
       </c>
     </row>
     <row r="173">
@@ -3259,7 +3709,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>475</v>
+        <v>550</v>
       </c>
     </row>
     <row r="174">
@@ -3267,7 +3717,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>476</v>
+        <v>551</v>
       </c>
     </row>
     <row r="175">
@@ -3275,7 +3725,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>477</v>
+        <v>552</v>
       </c>
     </row>
     <row r="176">
@@ -3283,7 +3733,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>478</v>
+        <v>553</v>
       </c>
     </row>
     <row r="177">
@@ -3291,7 +3741,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>479</v>
+        <v>554</v>
       </c>
     </row>
     <row r="178">
@@ -3299,7 +3749,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>480</v>
+        <v>555</v>
       </c>
     </row>
     <row r="179">
@@ -3307,7 +3757,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>481</v>
+        <v>556</v>
       </c>
     </row>
     <row r="180">
@@ -3315,7 +3765,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>482</v>
+        <v>557</v>
       </c>
     </row>
     <row r="181">
@@ -3323,7 +3773,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>483</v>
+        <v>558</v>
       </c>
     </row>
     <row r="182">
@@ -3331,7 +3781,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>484</v>
+        <v>559</v>
       </c>
     </row>
     <row r="183">
@@ -3339,7 +3789,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>485</v>
+        <v>560</v>
       </c>
     </row>
     <row r="184">
@@ -3347,7 +3797,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>486</v>
+        <v>561</v>
       </c>
     </row>
     <row r="185">
@@ -3355,7 +3805,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>487</v>
+        <v>562</v>
       </c>
     </row>
     <row r="186">
@@ -3363,7 +3813,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>488</v>
+        <v>563</v>
       </c>
     </row>
     <row r="187">
@@ -3371,7 +3821,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>489</v>
+        <v>564</v>
       </c>
     </row>
     <row r="188">
@@ -3379,7 +3829,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>490</v>
+        <v>565</v>
       </c>
     </row>
     <row r="189">
@@ -3387,7 +3837,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>491</v>
+        <v>566</v>
       </c>
     </row>
     <row r="190">
@@ -3395,7 +3845,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>492</v>
+        <v>567</v>
       </c>
     </row>
     <row r="191">
@@ -3403,7 +3853,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>493</v>
+        <v>568</v>
       </c>
     </row>
     <row r="192">
@@ -3411,7 +3861,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>494</v>
+        <v>569</v>
       </c>
     </row>
     <row r="193">
@@ -3419,7 +3869,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>495</v>
+        <v>570</v>
       </c>
     </row>
     <row r="194">
@@ -3427,7 +3877,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>496</v>
+        <v>571</v>
       </c>
     </row>
     <row r="195">
@@ -3435,7 +3885,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>497</v>
+        <v>572</v>
       </c>
     </row>
     <row r="196">
@@ -3443,7 +3893,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>498</v>
+        <v>573</v>
       </c>
     </row>
     <row r="197">
@@ -3451,7 +3901,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>499</v>
+        <v>574</v>
       </c>
     </row>
     <row r="198">
@@ -3459,7 +3909,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>500</v>
+        <v>575</v>
       </c>
     </row>
     <row r="199">
@@ -3467,7 +3917,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>501</v>
+        <v>576</v>
       </c>
     </row>
     <row r="200">
@@ -3475,7 +3925,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>502</v>
+        <v>577</v>
       </c>
     </row>
     <row r="201">
@@ -3483,7 +3933,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>503</v>
+        <v>578</v>
       </c>
     </row>
     <row r="202">
@@ -3491,7 +3941,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>504</v>
+        <v>579</v>
       </c>
     </row>
     <row r="203">
@@ -3499,7 +3949,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>505</v>
+        <v>580</v>
       </c>
     </row>
     <row r="204">
@@ -3507,7 +3957,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>506</v>
+        <v>581</v>
       </c>
     </row>
     <row r="205">
@@ -3515,7 +3965,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>507</v>
+        <v>582</v>
       </c>
     </row>
     <row r="206">
@@ -3523,7 +3973,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>508</v>
+        <v>583</v>
       </c>
     </row>
     <row r="207">
@@ -3531,7 +3981,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>509</v>
+        <v>584</v>
       </c>
     </row>
     <row r="208">
@@ -3539,7 +3989,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>510</v>
+        <v>585</v>
       </c>
     </row>
     <row r="209">
@@ -3547,7 +3997,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>511</v>
+        <v>586</v>
       </c>
     </row>
     <row r="210">
@@ -3555,7 +4005,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>512</v>
+        <v>587</v>
       </c>
     </row>
     <row r="211">
@@ -3563,7 +4013,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>513</v>
+        <v>588</v>
       </c>
     </row>
     <row r="212">
@@ -3571,7 +4021,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>514</v>
+        <v>589</v>
       </c>
     </row>
     <row r="213">
@@ -3579,7 +4029,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>515</v>
+        <v>590</v>
       </c>
     </row>
     <row r="214">
@@ -3587,7 +4037,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>516</v>
+        <v>591</v>
       </c>
     </row>
     <row r="215">
@@ -3595,7 +4045,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>517</v>
+        <v>592</v>
       </c>
     </row>
     <row r="216">
@@ -3603,7 +4053,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>518</v>
+        <v>593</v>
       </c>
     </row>
     <row r="217">
@@ -3611,7 +4061,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>519</v>
+        <v>594</v>
       </c>
     </row>
     <row r="218">
@@ -3619,7 +4069,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>520</v>
+        <v>595</v>
       </c>
     </row>
     <row r="219">
@@ -3627,7 +4077,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>521</v>
+        <v>596</v>
       </c>
     </row>
     <row r="220">
@@ -3635,7 +4085,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>522</v>
+        <v>597</v>
       </c>
     </row>
     <row r="221">
@@ -3643,7 +4093,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>523</v>
+        <v>598</v>
       </c>
     </row>
     <row r="222">
@@ -3651,7 +4101,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>524</v>
+        <v>599</v>
       </c>
     </row>
     <row r="223">
@@ -3659,7 +4109,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>525</v>
+        <v>600</v>
       </c>
     </row>
     <row r="224">
@@ -3667,7 +4117,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>526</v>
+        <v>601</v>
       </c>
     </row>
     <row r="225">
@@ -3675,7 +4125,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>527</v>
+        <v>602</v>
       </c>
     </row>
     <row r="226">
@@ -3683,7 +4133,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>528</v>
+        <v>603</v>
       </c>
     </row>
     <row r="227">
@@ -3691,7 +4141,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>529</v>
+        <v>604</v>
       </c>
     </row>
     <row r="228">
@@ -3699,7 +4149,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>530</v>
+        <v>605</v>
       </c>
     </row>
     <row r="229">
@@ -3707,7 +4157,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>531</v>
+        <v>606</v>
       </c>
     </row>
     <row r="230">
@@ -3715,7 +4165,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>532</v>
+        <v>607</v>
       </c>
     </row>
     <row r="231">
@@ -3723,7 +4173,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>533</v>
+        <v>608</v>
       </c>
     </row>
     <row r="232">
@@ -3731,7 +4181,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>534</v>
+        <v>609</v>
       </c>
     </row>
     <row r="233">
@@ -3739,7 +4189,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>535</v>
+        <v>610</v>
       </c>
     </row>
     <row r="234">
@@ -3747,7 +4197,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>536</v>
+        <v>611</v>
       </c>
     </row>
     <row r="235">
@@ -3755,7 +4205,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>537</v>
+        <v>612</v>
       </c>
     </row>
     <row r="236">
@@ -3763,7 +4213,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>538</v>
+        <v>613</v>
       </c>
     </row>
     <row r="237">
@@ -3771,7 +4221,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>539</v>
+        <v>614</v>
       </c>
     </row>
     <row r="238">
@@ -3779,7 +4229,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>540</v>
+        <v>615</v>
       </c>
     </row>
     <row r="239">
@@ -3787,7 +4237,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>541</v>
+        <v>616</v>
       </c>
     </row>
     <row r="240">
@@ -3795,7 +4245,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>542</v>
+        <v>617</v>
       </c>
     </row>
     <row r="241">
@@ -3803,7 +4253,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>543</v>
+        <v>618</v>
       </c>
     </row>
     <row r="242">
@@ -3811,7 +4261,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>544</v>
+        <v>619</v>
       </c>
     </row>
     <row r="243">
@@ -3819,7 +4269,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>545</v>
+        <v>620</v>
       </c>
     </row>
     <row r="244">
@@ -3827,7 +4277,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>546</v>
+        <v>621</v>
       </c>
     </row>
     <row r="245">
@@ -3835,7 +4285,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>547</v>
+        <v>622</v>
       </c>
     </row>
     <row r="246">
@@ -3843,7 +4293,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>548</v>
+        <v>623</v>
       </c>
     </row>
     <row r="247">
@@ -3851,7 +4301,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>549</v>
+        <v>624</v>
       </c>
     </row>
     <row r="248">
@@ -3859,7 +4309,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>550</v>
+        <v>625</v>
       </c>
     </row>
     <row r="249">
@@ -3867,7 +4317,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>551</v>
+        <v>626</v>
       </c>
     </row>
     <row r="250">
@@ -3875,7 +4325,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>552</v>
+        <v>627</v>
       </c>
     </row>
     <row r="251">
@@ -3883,7 +4333,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>553</v>
+        <v>628</v>
       </c>
     </row>
     <row r="252">
@@ -3891,7 +4341,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>554</v>
+        <v>629</v>
       </c>
     </row>
     <row r="253">
@@ -3899,7 +4349,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>555</v>
+        <v>630</v>
       </c>
     </row>
     <row r="254">
@@ -3907,7 +4357,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>556</v>
+        <v>631</v>
       </c>
     </row>
     <row r="255">
@@ -3915,7 +4365,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>557</v>
+        <v>632</v>
       </c>
     </row>
     <row r="256">
@@ -3923,7 +4373,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>558</v>
+        <v>633</v>
       </c>
     </row>
     <row r="257">
@@ -3931,7 +4381,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>559</v>
+        <v>634</v>
       </c>
     </row>
     <row r="258">
@@ -3939,7 +4389,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>560</v>
+        <v>635</v>
       </c>
     </row>
     <row r="259">
@@ -3947,7 +4397,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>561</v>
+        <v>636</v>
       </c>
     </row>
     <row r="260">
@@ -3955,7 +4405,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>562</v>
+        <v>637</v>
       </c>
     </row>
     <row r="261">
@@ -3963,7 +4413,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>563</v>
+        <v>638</v>
       </c>
     </row>
     <row r="262">
@@ -3971,7 +4421,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>564</v>
+        <v>639</v>
       </c>
     </row>
     <row r="263">
@@ -3979,7 +4429,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>565</v>
+        <v>640</v>
       </c>
     </row>
     <row r="264">
@@ -3987,7 +4437,7 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>566</v>
+        <v>641</v>
       </c>
     </row>
     <row r="265">
@@ -3995,7 +4445,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>567</v>
+        <v>642</v>
       </c>
     </row>
     <row r="266">
@@ -4003,7 +4453,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>568</v>
+        <v>643</v>
       </c>
     </row>
     <row r="267">
@@ -4011,7 +4461,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>569</v>
+        <v>644</v>
       </c>
     </row>
     <row r="268">
@@ -4019,7 +4469,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>570</v>
+        <v>645</v>
       </c>
     </row>
     <row r="269">
@@ -4027,7 +4477,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>571</v>
+        <v>646</v>
       </c>
     </row>
     <row r="270">
@@ -4035,7 +4485,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>572</v>
+        <v>647</v>
       </c>
     </row>
     <row r="271">
@@ -4043,7 +4493,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>573</v>
+        <v>648</v>
       </c>
     </row>
     <row r="272">
@@ -4051,7 +4501,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>574</v>
+        <v>649</v>
       </c>
     </row>
     <row r="273">
@@ -4059,7 +4509,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>575</v>
+        <v>650</v>
       </c>
     </row>
     <row r="274">
@@ -4067,7 +4517,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>576</v>
+        <v>651</v>
       </c>
     </row>
     <row r="275">
@@ -4075,7 +4525,7 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>577</v>
+        <v>652</v>
       </c>
     </row>
     <row r="276">
@@ -4083,7 +4533,7 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>578</v>
+        <v>653</v>
       </c>
     </row>
     <row r="277">
@@ -4091,7 +4541,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>579</v>
+        <v>654</v>
       </c>
     </row>
     <row r="278">
@@ -4099,7 +4549,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>580</v>
+        <v>655</v>
       </c>
     </row>
     <row r="279">
@@ -4107,7 +4557,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>581</v>
+        <v>656</v>
       </c>
     </row>
     <row r="280">
@@ -4115,7 +4565,7 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>582</v>
+        <v>657</v>
       </c>
     </row>
     <row r="281">
@@ -4123,7 +4573,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>583</v>
+        <v>658</v>
       </c>
     </row>
     <row r="282">
@@ -4131,7 +4581,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>584</v>
+        <v>659</v>
       </c>
     </row>
     <row r="283">
@@ -4139,7 +4589,7 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>585</v>
+        <v>660</v>
       </c>
     </row>
     <row r="284">
@@ -4147,7 +4597,7 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>586</v>
+        <v>661</v>
       </c>
     </row>
     <row r="285">
@@ -4155,7 +4605,7 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>587</v>
+        <v>662</v>
       </c>
     </row>
     <row r="286">
@@ -4163,7 +4613,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>588</v>
+        <v>663</v>
       </c>
     </row>
     <row r="287">
@@ -4171,7 +4621,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>589</v>
+        <v>664</v>
       </c>
     </row>
     <row r="288">
@@ -4179,7 +4629,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>590</v>
+        <v>665</v>
       </c>
     </row>
     <row r="289">
@@ -4187,7 +4637,7 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>591</v>
+        <v>666</v>
       </c>
     </row>
     <row r="290">
@@ -4195,7 +4645,7 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>592</v>
+        <v>667</v>
       </c>
     </row>
     <row r="291">
@@ -4203,7 +4653,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>593</v>
+        <v>668</v>
       </c>
     </row>
     <row r="292">
@@ -4211,7 +4661,7 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>594</v>
+        <v>669</v>
       </c>
     </row>
     <row r="293">
@@ -4219,7 +4669,7 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>595</v>
+        <v>670</v>
       </c>
     </row>
     <row r="294">
@@ -4227,7 +4677,7 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>596</v>
+        <v>671</v>
       </c>
     </row>
     <row r="295">
@@ -4235,7 +4685,7 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>597</v>
+        <v>672</v>
       </c>
     </row>
     <row r="296">
@@ -4243,7 +4693,7 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>598</v>
+        <v>673</v>
       </c>
     </row>
     <row r="297">
@@ -4251,7 +4701,7 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>599</v>
+        <v>674</v>
       </c>
     </row>
     <row r="298">
@@ -4259,7 +4709,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>600</v>
+        <v>675</v>
       </c>
     </row>
     <row r="299">
@@ -4267,7 +4717,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>601</v>
+        <v>676</v>
       </c>
     </row>
     <row r="300">
@@ -4275,7 +4725,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>602</v>
+        <v>677</v>
       </c>
     </row>
     <row r="301">
@@ -4283,7 +4733,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>603</v>
+        <v>678</v>
       </c>
     </row>
     <row r="302">
@@ -4291,7 +4741,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>604</v>
+        <v>679</v>
       </c>
     </row>
     <row r="303">
@@ -4299,7 +4749,7 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>605</v>
+        <v>680</v>
       </c>
     </row>
     <row r="304">
@@ -4307,7 +4757,607 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>606</v>
+        <v>681</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>304</v>
+      </c>
+      <c r="B305" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s">
+        <v>305</v>
+      </c>
+      <c r="B306" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s">
+        <v>306</v>
+      </c>
+      <c r="B307" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>307</v>
+      </c>
+      <c r="B308" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>308</v>
+      </c>
+      <c r="B309" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>309</v>
+      </c>
+      <c r="B310" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>310</v>
+      </c>
+      <c r="B311" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>311</v>
+      </c>
+      <c r="B312" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s">
+        <v>312</v>
+      </c>
+      <c r="B313" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>313</v>
+      </c>
+      <c r="B314" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s">
+        <v>314</v>
+      </c>
+      <c r="B315" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s">
+        <v>315</v>
+      </c>
+      <c r="B316" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s">
+        <v>316</v>
+      </c>
+      <c r="B317" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s">
+        <v>317</v>
+      </c>
+      <c r="B318" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s">
+        <v>318</v>
+      </c>
+      <c r="B319" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s">
+        <v>319</v>
+      </c>
+      <c r="B320" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s">
+        <v>320</v>
+      </c>
+      <c r="B321" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s">
+        <v>321</v>
+      </c>
+      <c r="B322" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s">
+        <v>322</v>
+      </c>
+      <c r="B323" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s">
+        <v>323</v>
+      </c>
+      <c r="B324" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s">
+        <v>324</v>
+      </c>
+      <c r="B325" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s">
+        <v>325</v>
+      </c>
+      <c r="B326" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s">
+        <v>326</v>
+      </c>
+      <c r="B327" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s">
+        <v>327</v>
+      </c>
+      <c r="B328" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s">
+        <v>328</v>
+      </c>
+      <c r="B329" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s">
+        <v>329</v>
+      </c>
+      <c r="B330" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s">
+        <v>330</v>
+      </c>
+      <c r="B331" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s">
+        <v>331</v>
+      </c>
+      <c r="B332" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s">
+        <v>332</v>
+      </c>
+      <c r="B333" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s">
+        <v>333</v>
+      </c>
+      <c r="B334" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s">
+        <v>334</v>
+      </c>
+      <c r="B335" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s">
+        <v>335</v>
+      </c>
+      <c r="B336" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s">
+        <v>336</v>
+      </c>
+      <c r="B337" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s">
+        <v>337</v>
+      </c>
+      <c r="B338" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s">
+        <v>338</v>
+      </c>
+      <c r="B339" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s">
+        <v>339</v>
+      </c>
+      <c r="B340" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s">
+        <v>340</v>
+      </c>
+      <c r="B341" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s">
+        <v>341</v>
+      </c>
+      <c r="B342" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s">
+        <v>342</v>
+      </c>
+      <c r="B343" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s">
+        <v>343</v>
+      </c>
+      <c r="B344" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s">
+        <v>344</v>
+      </c>
+      <c r="B345" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s">
+        <v>345</v>
+      </c>
+      <c r="B346" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s">
+        <v>346</v>
+      </c>
+      <c r="B347" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s">
+        <v>347</v>
+      </c>
+      <c r="B348" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s">
+        <v>348</v>
+      </c>
+      <c r="B349" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s">
+        <v>349</v>
+      </c>
+      <c r="B350" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s">
+        <v>350</v>
+      </c>
+      <c r="B351" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s">
+        <v>351</v>
+      </c>
+      <c r="B352" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s">
+        <v>352</v>
+      </c>
+      <c r="B353" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s">
+        <v>353</v>
+      </c>
+      <c r="B354" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s">
+        <v>354</v>
+      </c>
+      <c r="B355" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s">
+        <v>355</v>
+      </c>
+      <c r="B356" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s">
+        <v>356</v>
+      </c>
+      <c r="B357" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s">
+        <v>357</v>
+      </c>
+      <c r="B358" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s">
+        <v>358</v>
+      </c>
+      <c r="B359" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s">
+        <v>359</v>
+      </c>
+      <c r="B360" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s">
+        <v>360</v>
+      </c>
+      <c r="B361" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s">
+        <v>361</v>
+      </c>
+      <c r="B362" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s">
+        <v>362</v>
+      </c>
+      <c r="B363" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s">
+        <v>363</v>
+      </c>
+      <c r="B364" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s">
+        <v>364</v>
+      </c>
+      <c r="B365" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s">
+        <v>365</v>
+      </c>
+      <c r="B366" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s">
+        <v>366</v>
+      </c>
+      <c r="B367" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s">
+        <v>367</v>
+      </c>
+      <c r="B368" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s">
+        <v>368</v>
+      </c>
+      <c r="B369" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s">
+        <v>369</v>
+      </c>
+      <c r="B370" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s">
+        <v>370</v>
+      </c>
+      <c r="B371" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s">
+        <v>371</v>
+      </c>
+      <c r="B372" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s">
+        <v>372</v>
+      </c>
+      <c r="B373" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s">
+        <v>373</v>
+      </c>
+      <c r="B374" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s">
+        <v>374</v>
+      </c>
+      <c r="B375" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s">
+        <v>375</v>
+      </c>
+      <c r="B376" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s">
+        <v>376</v>
+      </c>
+      <c r="B377" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s">
+        <v>377</v>
+      </c>
+      <c r="B378" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s">
+        <v>378</v>
+      </c>
+      <c r="B379" t="s">
+        <v>756</v>
       </c>
     </row>
   </sheetData>
